--- a/EXCEL/personalegrupper.xlsx
+++ b/EXCEL/personalegrupper.xlsx
@@ -72,7 +72,7 @@
     <ns0:t>Datasæt 02 2020</ns0:t>
   </ns0:si>
   <ns0:si>
-    <ns0:t>Kørsel 7.4.2026 12.44.38</ns0:t>
+    <ns0:t>Kørsel 7.4.2026 12.45.15</ns0:t>
   </ns0:si>
   <ns0:si>
     <ns0:t>Undergrænse: 5</ns0:t>
@@ -201,7 +201,7 @@
     <ns0:t>Læger, trin 2</ns0:t>
   </ns0:si>
   <ns0:si>
-    <ns0:t>Kørsel 7.4.2026 12.44.41</ns0:t>
+    <ns0:t>Kørsel 7.4.2026 12.45.18</ns0:t>
   </ns0:si>
   <ns0:si>
     <ns0:t>05513 Specialister</ns0:t>
@@ -297,7 +297,7 @@
     <ns0:t>Sygeplejersker.</ns0:t>
   </ns0:si>
   <ns0:si>
-    <ns0:t>Kørsel 7.4.2026 12.44.44</ns0:t>
+    <ns0:t>Kørsel 7.4.2026 12.45.21</ns0:t>
   </ns0:si>
   <ns0:si>
     <ns0:t>29601 Atypiske stillinger</ns0:t>
